--- a/reports/history/build-2/Failed_Test_Cases.xlsx
+++ b/reports/history/build-2/Failed_Test_Cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="44">
   <si>
     <t>Test ID</t>
   </si>
@@ -34,73 +34,115 @@
     <t>Failure Reason</t>
   </si>
   <si>
-    <t>TC_VAL_014</t>
+    <t>TC_AUTH_008</t>
+  </si>
+  <si>
+    <t>Authentication</t>
+  </si>
+  <si>
+    <t>Authentication Verification - Case 8</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>FAILED</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 7</t>
+  </si>
+  <si>
+    <t>TC_NAV_006</t>
+  </si>
+  <si>
+    <t>Navigation</t>
+  </si>
+  <si>
+    <t>Navigation Verification - Case 6</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 115</t>
+  </si>
+  <si>
+    <t>TC_NAV_007</t>
+  </si>
+  <si>
+    <t>Navigation Verification - Case 7</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 116</t>
+  </si>
+  <si>
+    <t>TC_CRUD_032</t>
+  </si>
+  <si>
+    <t>CRUD Operations</t>
+  </si>
+  <si>
+    <t>CRUD Operations Verification - Case 32</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 231</t>
+  </si>
+  <si>
+    <t>TC_CRUD_036</t>
+  </si>
+  <si>
+    <t>CRUD Operations Verification - Case 36</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 235</t>
+  </si>
+  <si>
+    <t>TC_VAL_025</t>
   </si>
   <si>
     <t>Input Validation</t>
   </si>
   <si>
-    <t>Input Validation Verification - Case 14</t>
-  </si>
-  <si>
-    <t>Low</t>
-  </si>
-  <si>
-    <t>FAILED</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 293</t>
-  </si>
-  <si>
-    <t>TC_ERR_001</t>
+    <t>Input Validation Verification - Case 25</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 304</t>
+  </si>
+  <si>
+    <t>TC_ERR_011</t>
   </si>
   <si>
     <t>Error Handling</t>
   </si>
   <si>
-    <t>Error Handling Verification - Case 1</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 320</t>
-  </si>
-  <si>
-    <t>TC_SESS_010</t>
-  </si>
-  <si>
-    <t>Session Management</t>
-  </si>
-  <si>
-    <t>Session Management Verification - Case 10</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 349</t>
-  </si>
-  <si>
-    <t>TC_PERF_017</t>
-  </si>
-  <si>
-    <t>Performance Smoke Tests</t>
-  </si>
-  <si>
-    <t>Performance Smoke Tests Verification - Case 17</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 456</t>
-  </si>
-  <si>
-    <t>TC_REGR_001</t>
+    <t>Error Handling Verification - Case 11</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 330</t>
+  </si>
+  <si>
+    <t>TC_ERR_014</t>
+  </si>
+  <si>
+    <t>Error Handling Verification - Case 14</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 333</t>
+  </si>
+  <si>
+    <t>TC_REGR_050</t>
   </si>
   <si>
     <t>Regression Suite</t>
   </si>
   <si>
-    <t>Regression Suite Verification - Case 1</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 460</t>
+    <t>Regression Suite Verification - Case 50</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 509</t>
   </si>
 </sst>
 </file>
@@ -491,11 +533,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
     <col min="4" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="23" customWidth="1"/>
@@ -542,7 +584,7 @@
         <v>11</v>
       </c>
       <c r="F2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G2" t="s">
         <v>12</v>
@@ -565,7 +607,7 @@
         <v>11</v>
       </c>
       <c r="F3">
-        <v>254</v>
+        <v>299</v>
       </c>
       <c r="G3" t="s">
         <v>17</v>
@@ -576,19 +618,19 @@
         <v>18</v>
       </c>
       <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
         <v>19</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>20</v>
       </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
       <c r="E4" t="s">
         <v>11</v>
       </c>
       <c r="F4">
-        <v>296</v>
+        <v>206</v>
       </c>
       <c r="G4" t="s">
         <v>21</v>
@@ -611,7 +653,7 @@
         <v>11</v>
       </c>
       <c r="F5">
-        <v>180</v>
+        <v>212</v>
       </c>
       <c r="G5" t="s">
         <v>25</v>
@@ -622,10 +664,10 @@
         <v>26</v>
       </c>
       <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
         <v>27</v>
-      </c>
-      <c r="C6" t="s">
-        <v>28</v>
       </c>
       <c r="D6" t="s">
         <v>16</v>
@@ -634,10 +676,102 @@
         <v>11</v>
       </c>
       <c r="F6">
-        <v>202</v>
+        <v>267</v>
       </c>
       <c r="G6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>29</v>
+      </c>
+      <c r="B7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7">
+        <v>174</v>
+      </c>
+      <c r="G7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8">
+        <v>103</v>
+      </c>
+      <c r="G8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9">
+        <v>289</v>
+      </c>
+      <c r="G9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10">
+        <v>132</v>
+      </c>
+      <c r="G10" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
